--- a/Scripts/Examples/Matrix template.xlsx
+++ b/Scripts/Examples/Matrix template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gijbelsb\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gijbelsb\Downloads\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3008D3B-1EED-4A63-8F3D-CE6EDD509974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE82312-BDE2-48AB-B5D4-9D3D52B8A813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33810" yWindow="1965" windowWidth="17820" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Permissions" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
   <si>
     <t>F</t>
   </si>
@@ -55,9 +55,6 @@
     <t>ComputerName</t>
   </si>
   <si>
-    <t>SiteName</t>
-  </si>
-  <si>
     <t>SiteCode</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
   </si>
   <si>
     <t>Brussels Auditor</t>
-  </si>
-  <si>
-    <t>Brussels</t>
   </si>
   <si>
     <t>Fix</t>
@@ -288,13 +282,7 @@
     <t>BXL</t>
   </si>
   <si>
-    <t>Genk</t>
-  </si>
-  <si>
     <t>GNK</t>
-  </si>
-  <si>
-    <t>JobsAtOnce</t>
   </si>
   <si>
     <t>COMPUTER1</t>
@@ -1066,19 +1054,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="34" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1116,7 +1104,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Test"/>
@@ -2091,41 +2079,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="5.26953125" customWidth="1"/>
-    <col min="4" max="5" width="5.26953125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" style="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="7.26953125" style="6" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="5" width="5.28515625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" style="6" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="92" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="91.5" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B1" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="E1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>48</v>
-      </c>
       <c r="F1" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="6" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="6" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="9"/>
@@ -2133,30 +2121,30 @@
       <c r="E2" s="34"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:7" s="6" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" s="6" customFormat="1" ht="92.25" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="6" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="40" t="s">
         <v>5</v>
       </c>
@@ -2179,12 +2167,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16" t="s">
@@ -2200,13 +2188,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>1</v>
@@ -2221,9 +2209,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="18"/>
@@ -2240,9 +2228,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B8" s="64"/>
       <c r="C8" s="65"/>
@@ -2255,9 +2243,9 @@
       <c r="F8" s="67"/>
       <c r="G8" s="68"/>
     </row>
-    <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="63" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B9" s="64"/>
       <c r="C9" s="65"/>
@@ -2270,15 +2258,15 @@
       <c r="F9" s="67"/>
       <c r="G9" s="68"/>
     </row>
-    <row r="10" spans="1:7" s="5" customFormat="1" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="5" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="20"/>
       <c r="D10" s="20"/>
       <c r="E10" s="26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="39" t="s">
         <v>1</v>
@@ -2299,205 +2287,171 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.7265625" style="73" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" style="73" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G3" s="72" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="72"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="70"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="72"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="70"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="72"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="70"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="72"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D7" s="1"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="70"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="72"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="1"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="70"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="72"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="4"/>
-      <c r="C10" s="1"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="72"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="72"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
-      <c r="C12" s="1"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="72"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="70"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="1"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="70"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="70"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="70"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="72"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="4"/>
+      <c r="F13" s="70"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="72"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="70"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="72"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D15" s="3"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="70"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="G16" s="72"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F16" s="70"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
+      <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="72"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="70"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
+      <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="72"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="70"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="72"/>
+      <c r="F19" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2508,55 +2462,55 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D6C2115-40D8-41A2-87C6-F219BE67F73D}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.1796875" style="5"/>
+    <col min="1" max="1" width="16.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="62" t="s">
         <v>36</v>
-      </c>
-      <c r="D2" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="62" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2571,19 +2525,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.453125" style="46" customWidth="1"/>
-    <col min="2" max="2" width="60.1796875" style="46" customWidth="1"/>
-    <col min="3" max="3" width="79.81640625" style="46" customWidth="1"/>
-    <col min="4" max="16384" width="9.1796875" style="46"/>
+    <col min="1" max="1" width="10.42578125" style="46" customWidth="1"/>
+    <col min="2" max="2" width="60.140625" style="46" customWidth="1"/>
+    <col min="3" max="3" width="79.85546875" style="46" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="46"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="70"/>
+    <row r="1" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="73"/>
       <c r="C1" s="47"/>
       <c r="D1" s="48"/>
       <c r="E1" s="48"/>
@@ -2600,12 +2554,12 @@
       <c r="P1" s="48"/>
       <c r="Q1" s="48"/>
     </row>
-    <row r="2" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="48"/>
@@ -2623,10 +2577,10 @@
       <c r="P2" s="48"/>
       <c r="Q2" s="48"/>
     </row>
-    <row r="3" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="52"/>
       <c r="B3" s="53" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="48"/>
       <c r="E3" s="48"/>
@@ -2643,12 +2597,12 @@
       <c r="P3" s="48"/>
       <c r="Q3" s="48"/>
     </row>
-    <row r="4" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="48"/>
       <c r="E4" s="48"/>
@@ -2665,12 +2619,12 @@
       <c r="P4" s="48"/>
       <c r="Q4" s="48"/>
     </row>
-    <row r="5" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" s="48"/>
       <c r="E5" s="48"/>
@@ -2687,12 +2641,12 @@
       <c r="P5" s="48"/>
       <c r="Q5" s="48"/>
     </row>
-    <row r="6" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="57" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" s="48"/>
       <c r="E6" s="48"/>
@@ -2709,12 +2663,12 @@
       <c r="P6" s="48"/>
       <c r="Q6" s="48"/>
     </row>
-    <row r="7" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="58" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
@@ -2731,12 +2685,12 @@
       <c r="P7" s="48"/>
       <c r="Q7" s="48"/>
     </row>
-    <row r="8" spans="1:17" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2749,7 +2703,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2802,9 +2758,7 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2817,9 +2771,16 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB8DE14-8EA8-40DE-9709-400EEAA9E777}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE7EF8E-BF67-4561-A935-3685C3E9EC35}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2840,16 +2801,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE7EF8E-BF67-4561-A935-3685C3E9EC35}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB8DE14-8EA8-40DE-9709-400EEAA9E777}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2860,4 +2814,10 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{69c428b0-0db1-4300-b2dd-9484759bca92}" enabled="1" method="Standard" siteId="{57952406-af28-43c8-b4de-a4e06f57476d}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Scripts/Examples/Matrix template.xlsx
+++ b/Scripts/Examples/Matrix template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gijbelsb\Downloads\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE82312-BDE2-48AB-B5D4-9D3D52B8A813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6924A6DC-5608-43A7-BA57-D9067AEA4462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32250" yWindow="1785" windowWidth="21600" windowHeight="11235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Permissions" sheetId="4" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
   <si>
     <t>F</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>COMPUTER2</t>
+  </si>
+  <si>
+    <t>ApplyDefaultPermissions</t>
   </si>
 </sst>
 </file>
@@ -2287,17 +2290,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2313,11 +2317,14 @@
       <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="69" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2333,11 +2340,14 @@
       <c r="E2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="70" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -2353,105 +2363,120 @@
       <c r="E3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="70" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="70"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F4" s="4"/>
+      <c r="G4" s="70"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="1"/>
       <c r="D5" s="3"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="70"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5" s="4"/>
+      <c r="G5" s="70"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="70"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6" s="4"/>
+      <c r="G6" s="70"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="4"/>
       <c r="D7" s="1"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="70"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="4"/>
+      <c r="G7" s="70"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
       <c r="D8" s="1"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="70"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8" s="4"/>
+      <c r="G8" s="70"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="70"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9" s="4"/>
+      <c r="G9" s="70"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" s="1"/>
       <c r="D10" s="3"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="70"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="4"/>
+      <c r="G10" s="70"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
-      <c r="F11" s="70"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11" s="4"/>
+      <c r="G11" s="70"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12" s="1"/>
       <c r="D12" s="3"/>
       <c r="E12" s="4"/>
-      <c r="F12" s="70"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12" s="4"/>
+      <c r="G12" s="70"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="70"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F13" s="4"/>
+      <c r="G13" s="70"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B14" s="4"/>
       <c r="D14" s="3"/>
       <c r="E14" s="4"/>
-      <c r="F14" s="70"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F14" s="4"/>
+      <c r="G14" s="70"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B15" s="4"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="70"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="4"/>
+      <c r="G15" s="70"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B16" s="4"/>
-      <c r="F16" s="70"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="G16" s="70"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="4"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="70"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="G17" s="70"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="4"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="70"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="G18" s="70"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2703,9 +2728,7 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2758,7 +2781,9 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<LongProperties xmlns="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2771,16 +2796,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE7EF8E-BF67-4561-A935-3685C3E9EC35}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB8DE14-8EA8-40DE-9709-400EEAA9E777}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2801,9 +2819,16 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB8DE14-8EA8-40DE-9709-400EEAA9E777}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AE7EF8E-BF67-4561-A935-3685C3E9EC35}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/longProperties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
